--- a/gsp-audit/2026-07/GSP Self Declaration and Assessment Checklist _ v1.1.xlsx
+++ b/gsp-audit/2026-07/GSP Self Declaration and Assessment Checklist _ v1.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neeraj/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neeraj/space/Code/blowbits-docs/gsp-audit/2026-07/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDD44DD-AE2A-E949-9B41-96657CF13716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2354CFE5-3FED-3B48-B171-03855C7CE16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="29920" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Version Control Sheet " sheetId="5" r:id="rId1"/>
@@ -919,11 +919,6 @@
     <t>Since no external third-party ASPs are onboarded on the platform, no list changes have occurred. The one-week reporting rule is pre-defined and will be followed if any external ASP configuration changes in the future.</t>
   </si>
   <si>
-    <t>Request mapping is executed entirely server-side based on the identifier of each incoming API request. When a request hits the gateway, the GSP layer validates the HTTP Basic Authentication credentials presented in the header. The verified identity parameter is immediately used by the server runtime to dynamically look up and map the request context to the corresponding, isolated GSP credential set inside the secure environment memory block. This runtime mapping ensures that the incoming API request is securely processed and routed to the GST System over an encrypted HTTPS connection without exposing any backend credential records.
-Evidence Filed As: 
-Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
-  </si>
-  <si>
     <t>The GSP layer enforces strict authentication and authorisation controls at the outer gateway edge before processing any incoming API request. All inbound communication requires HTTPS secured with TLS 1.2 or higher to protect transit integrity. The gateway evaluates the HTTP Basic Authentication credentials presented in the request header against verified configuration states. Requests bearing invalid credentials, disabled identifiers, or unassigned permissions are immediately rejected at the perimeter before any routing or interaction with the backend GST System is initiated.
 Evidence Filed As: 
 Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
@@ -957,232 +952,126 @@
 POL001-Information Security Policy.pdf</t>
   </si>
   <si>
-    <t>Secure MPLS connectivity for direct integration with the GST System is provisioned via Tata Communications Limited (TCL), the designated Internet Service Provider (ISP). The dedicated network connection is maintained and monitored in accordance with official GSTN connectivity guidelines to ensure reliable, high-availability data routing. The organisation maintains a valid enterprise service level agreement with the provider covering operational support and bandwidth availability for the production GSP gateway environment.
+    <t>Yes. The organisation maintains an active ISO/IEC 27001 certified Information Security Management System (ISMS) that enforces a continual improvement lifecycle. All corporate security policies (POL-001 to POL-012) and Standard Operating Procedures (SOP-001 to SOP-005) undergo formal scheduled reviews and updates at least annually, or in response to major regulatory variations, vulnerability assessments, and evolving threat vectors. This review process ensures that the framework remains continuously updated in line with global best practices and security baselines.
+Evidence Filed As: 
+POL001-Information Security Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The GSP production environment enforces strict host-level protection on all endpoints that connect to the GSTN network. The endpoint scope is limited entirely to automated production Linux servers; no local workstations, client laptops, or mobile devices are permitted to connect to the GSTN network interface. These production servers are secured using minimal OS software installation, strict server-side firewalls (AWS Security Groups), and host-level hardening configurations. The entire endpoint environment is continuously monitored for anomalies via our centralised telemetry framework.
 Evidence Filed As: 
 POL004-Network Security Policy.pdf
 Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
   </si>
   <si>
-    <t>Yes. The organisation maintains an active ISO/IEC 27001 certified Information Security Management System (ISMS) that enforces a continual improvement lifecycle. All corporate security policies (POL-001 to POL-012) and Standard Operating Procedures (SOP-001 to SOP-005) undergo formal scheduled reviews and updates at least annually, or in response to major regulatory variations, vulnerability assessments, and evolving threat vectors. This review process ensures that the framework remains continuously updated in line with global best practices and security baselines.
-Evidence Filed As: 
-POL001-Information Security Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The GSP production environment enforces strict host-level protection on all endpoints that connect to the GSTN network. The endpoint scope is limited entirely to automated production Linux servers; no local workstations, client laptops, or mobile devices are permitted to connect to the GSTN network interface. These production servers are secured using minimal OS software installation, strict server-side firewalls (AWS Security Groups), and host-level hardening configurations. The entire endpoint environment is continuously monitored for anomalies via our centralised telemetry framework.
+    <t>Yes. The GSP production endpoints (Linux servers) are continuously updated and monitored for security compliance. Operating system security patches are regularly evaluated and applied to mitigate newly identified vulnerabilities. System auth logs, server health metrics, and runtime access events are streamed live to the central telemetry framework (managed via Loki and Grafana). This operational data is continuously monitored by authorised personnel to detect anomalies, unauthorized access attempts, or potential security incidents immediately.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf</t>
+  </si>
+  <si>
+    <t>Traditional host-level anti-malware software is not deployed on the minimalist production Linux application servers. Instead, malware protection is enforced at the network edge via the perimeter firewall, which operates an active Intrusion Detection and Prevention System (IPS/IDS). This network security layer is periodically updated with the latest Emerging Threats (ET) Malware signature rule sets, ensuring continuous protection against evolving threat vectors before they can reach the gateway environment.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The GSP gateway intercepts and inspects all incoming network traffic at the outer perimeter before it can interface with internal systems or the GSTN network. Real-time threat detection is handled by the perimeter firewall's active IPS/IDS layer, which scans incoming packet streams for signature patterns matching viruses, trojans, worms, and other malware types. Any traffic containing known malicious patterns is blocked instantly at the boundary.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Containment procedures are triggered via real-time alerts from our network boundary. When the perimeter firewall's active IDS layer flags an anomalous signature or potential network threat, an immediate alert is generated for our system administrators. Following our incident response procedure, the administrative team reviews the alert and manually updates the firewall rules to isolate, block, or drop the offending source IP address, preventing any further interaction with the gateway environment.
+Evidence Filed As: 
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation tracks emerging vulnerabilities and infrastructure security risks by reviewing trusted external security sources and official public advisories. This intake includes monitoring security bulletins from CERT-In (Indian Computer Emergency Response Team), GSTN announcements, and upstream software vendor security feeds. Reviewing these external bulletins allows the administration team to stay updated on critical zero-day vulnerabilities or connectivity updates that might impact the GSP gateway environment.
+Evidence Filed As: 
+SOP008-Patch &amp; Security Update Procedure.pdf
+POL009-Vulnerability Management Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Incoming threat intelligence and external security advisories are actively reviewed by the administration team to harden the gateway infrastructure. When critical risks, malicious IP blocks, or zero-day vulnerabilities are flagged in external bulletins, the team evaluates their relevance to the environment. Verified threat indicators are then incorporated directly into the security framework by updating the network firewall rule sets, adjusting the network IDS alert parameters, or applying targeted security configurations to the production servers.
+Evidence Filed As: 
+SOP008-Patch &amp; Security Update Procedure.pdf
+POL009-Vulnerability Management Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The gateway environment is continuously monitored against vendor vulnerability releases to ensure security updates are processed without operational delay. Security updates are prioritized into distinct risk categories based on severity and direct impact on production infrastructure. Critical vulnerabilities undergo an expedited risk assessment for swift patch deployment, while lower-severity patches are consolidated and applied during scheduled infrastructure maintenance windows. Post-deployment, all systems are monitored to verify operational stability and continued protection.
+Evidence Filed As: 
+SOP008-Patch &amp; Security Update Procedure.pdf
+POL009-Vulnerability Management Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Software updates and security patches issued by upstream vendors and operating system repositories are evaluated and installed promptly as part of our patch management cycle. The administration team tracks vendor release streams to identify applicable security updates. Critical updates are prioritized for swift deployment, while routine stability patches are grouped and executed during scheduled maintenance windows to prevent version lag while ensuring continuous platform reliability.
+Evidence Filed As: 
+SOP008-Patch &amp; Security Update Procedure.pdf
+POL009-Vulnerability Management Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation maintains a formally documented Incident Response Plan that outlines procedures for detecting, containing, and resolving security incidents or data breaches. This framework covers step-by-step containment protocols managed by our administrative team and provides explicit coordination guidelines for reporting relevant security events to the GSTN helpdesk through designated communication channels. All security events are logged and evaluated to continuously patch and reinforce perimeter defenses.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The core technical team responsible for operating and managing the GSP gateway infrastructure functions directly as the incident handling unit. Team readiness and swift mitigation capabilities are maintained natively through close collaboration and regular technical reviews of software documentation, vendor patches, and threat bulletins. Because the team directly owns the infrastructure, members are fully equipped to instantly deploy firewall modifications or adjust network IDS settings to neutralize security events or anomalies without administrative delay.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation maintains a formal incident response procedure that explicitly outlines operational roles, escalation pathways, and remediation steps. Given our flat team structure, responsibilities are clearly divided: the technical members hold full ownership over real-time infrastructure isolation, monitoring, and patch implementation, while management handles external communication, compliance tracking, and direct coordination with the GSTN authorities. This division ensures rapid containment without administrative overhead.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Dedicated security incident response roles are formally assigned within the core technical and operations team to manage and remediate platform events. The technical role is directly accountable for executing containment, system isolation, and path tracking, while the management role holds responsibility for escalation oversight and external reporting. This role-based ownership ensures that trained personnel are permanently designated to respond to infrastructure alerts without the overhead of an independent department.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Security events are categorized into distinct severity levels—Critical, High, Medium, and Low—based on their potential impact on platform availability and connectivity. This categorization allows our core technical team to prioritize response actions instantly, ensuring that any anomaly threatening gateway operations is treated as a high-priority event requiring immediate containment. Over the past year of operations, no material security incidents or data breaches impacting the gateway environment or connectivity have occurred.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation periodically validates its incident handling readiness through targeted technical walkthroughs and infrastructure resilience testing. Rather than conducting large corporate mock drills, our compact technical team reviews threat scenarios directly against the production layout. This includes simulating network anomalies to verify that the IDS alerts trigger properly, evaluating firewall adjustment speed, and testing service availability zones to ensure the platform remains stable and responsive during emergency mitigation.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation ensures that all non-conformities (NCs) or observations raised during audits or assessments are tracked and closed within the mandated 45-day window, or as specified by GSTN. Any reported observation is directly reviewed by the core technical team to implement necessary security or infrastructure fixes. The remediation steps are thoroughly verified post-implementation to guarantee compliance and ensure swift, permanent closure of the item.
+Evidence Filed As: 
+POL009-Vulnerability Management Policy.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The core technical team is directly responsible for managing, updating, and maintaining the firewall rule sets. Configurations are controlled electronically via the firewall administration layer and host-level security groups. Any proposed rule change undergoes an internal peer-review process within the team to ensure security alignment before deployment. The running configuration is reviewed periodically to identify and prune redundant or obsolete rules, with automated configuration versioning providing a clean audit trail.
 Evidence Filed As: 
 POL004-Network Security Policy.pdf
 Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
   </si>
   <si>
-    <t>Yes. The GSP production endpoints (Linux servers) are continuously updated and monitored for security compliance. Operating system security patches are regularly evaluated and applied to mitigate newly identified vulnerabilities. System auth logs, server health metrics, and runtime access events are streamed live to the central telemetry framework (managed via Loki and Grafana). This operational data is continuously monitored by authorised personnel to detect anomalies, unauthorized access attempts, or potential security incidents immediately.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf</t>
-  </si>
-  <si>
-    <t>Traditional host-level anti-malware software is not deployed on the minimalist production Linux application servers. Instead, malware protection is enforced at the network edge via the perimeter firewall, which operates an active Intrusion Detection and Prevention System (IPS/IDS). This network security layer is periodically updated with the latest Emerging Threats (ET) Malware signature rule sets, ensuring continuous protection against evolving threat vectors before they can reach the gateway environment.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The GSP gateway intercepts and inspects all incoming network traffic at the outer perimeter before it can interface with internal systems or the GSTN network. Real-time threat detection is handled by the perimeter firewall's active IPS/IDS layer, which scans incoming packet streams for signature patterns matching viruses, trojans, worms, and other malware types. Any traffic containing known malicious patterns is blocked instantly at the boundary.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Containment procedures are triggered via real-time alerts from our network boundary. When the perimeter firewall's active IDS layer flags an anomalous signature or potential network threat, an immediate alert is generated for our system administrators. Following our incident response procedure, the administrative team reviews the alert and manually updates the firewall rules to isolate, block, or drop the offending source IP address, preventing any further interaction with the gateway environment.
-Evidence Filed As: 
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation enforces a streamlined incident response procedure to manage security events flagged by the network IDS layer. Once an alert is verified as a valid security threat by our administration team, containment protocols are launched immediately to patch and protect the perimeter. If an event impacts or threatens the integrity of external connections, a formal notification protocol is initiated to communicate the operational details directly to the GSTN helpdesk or technical support authorities through designated security management channels.
-Evidence Filed As: 
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation tracks emerging vulnerabilities and infrastructure security risks by reviewing trusted external security sources and official public advisories. This intake includes monitoring security bulletins from CERT-In (Indian Computer Emergency Response Team), GSTN announcements, and upstream software vendor security feeds. Reviewing these external bulletins allows the administration team to stay updated on critical zero-day vulnerabilities or connectivity updates that might impact the GSP gateway environment.
-Evidence Filed As: 
-SOP008-Patch &amp; Security Update Procedure.pdf
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The GSP production environment monitors for potential Command-and-Control (C&amp;C) activity through strict network isolation and active signature tracking. The infrastructure is segmented into distinct, isolated security zones (DMZ, Application, and Database layers) using AWS Security Groups to prevent lateral exposure across systems.
-Traffic across these network zones is continuously analyzed by the network IDS layer, which is explicitly configured with active botcc (Botnet Command and Control) signature rules. This mechanism inspects network packet streams and triggers immediate, high-priority administrative alerts if any data patterns match known malicious C&amp;C infrastructure.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Incoming threat intelligence and external security advisories are actively reviewed by the administration team to harden the gateway infrastructure. When critical risks, malicious IP blocks, or zero-day vulnerabilities are flagged in external bulletins, the team evaluates their relevance to the environment. Verified threat indicators are then incorporated directly into the security framework by updating the network firewall rule sets, adjusting the network IDS alert parameters, or applying targeted security configurations to the production servers.
-Evidence Filed As: 
-SOP008-Patch &amp; Security Update Procedure.pdf
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation enforces a structured patch management program to ensure all production servers and infrastructure components receive regular security updates. Security advisories from operating system vendors, software dependencies, and authoritative bodies like CERT-In are periodically reviewed by the administration team to evaluate relevance and risk. Applicable patches are verified and tested in a controlled environment before being deployed during scheduled maintenance windows to maintain system stability and platform availability.
-Evidence Filed As: 
-SOP008-Patch &amp; Security Update Procedure.pdf
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The gateway environment is continuously monitored against vendor vulnerability releases to ensure security updates are processed without operational delay. Security updates are prioritized into distinct risk categories based on severity and direct impact on production infrastructure. Critical vulnerabilities undergo an expedited risk assessment for swift patch deployment, while lower-severity patches are consolidated and applied during scheduled infrastructure maintenance windows. Post-deployment, all systems are monitored to verify operational stability and continued protection.
-Evidence Filed As: 
-SOP008-Patch &amp; Security Update Procedure.pdf
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Software updates and security patches issued by upstream vendors and operating system repositories are evaluated and installed promptly as part of our patch management cycle. The administration team tracks vendor release streams to identify applicable security updates. Critical updates are prioritized for swift deployment, while routine stability patches are grouped and executed during scheduled maintenance windows to prevent version lag while ensuring continuous platform reliability.
-Evidence Filed As: 
-SOP008-Patch &amp; Security Update Procedure.pdf
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation maintains a formally documented Incident Response Plan that outlines procedures for detecting, containing, and resolving security incidents or data breaches. This framework covers step-by-step containment protocols managed by our administrative team and provides explicit coordination guidelines for reporting relevant security events to the GSTN helpdesk through designated communication channels. All security events are logged and evaluated to continuously patch and reinforce perimeter defenses.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The core technical team responsible for operating and managing the GSP gateway infrastructure functions directly as the incident handling unit. Team readiness and swift mitigation capabilities are maintained natively through close collaboration and regular technical reviews of software documentation, vendor patches, and threat bulletins. Because the team directly owns the infrastructure, members are fully equipped to instantly deploy firewall modifications or adjust network IDS settings to neutralize security events or anomalies without administrative delay.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation maintains a formal incident response procedure that explicitly outlines operational roles, escalation pathways, and remediation steps. Given our flat team structure, responsibilities are clearly divided: the technical members hold full ownership over real-time infrastructure isolation, monitoring, and patch implementation, while management handles external communication, compliance tracking, and direct coordination with the GSTN authorities. This division ensures rapid containment without administrative overhead.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Dedicated security incident response roles are formally assigned within the core technical and operations team to manage and remediate platform events. The technical role is directly accountable for executing containment, system isolation, and path tracking, while the management role holds responsibility for escalation oversight and external reporting. This role-based ownership ensures that trained personnel are permanently designated to respond to infrastructure alerts without the overhead of an independent department.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Security events are categorized into distinct severity levels—Critical, High, Medium, and Low—based on their potential impact on platform availability and connectivity. This categorization allows our core technical team to prioritize response actions instantly, ensuring that any anomaly threatening gateway operations is treated as a high-priority event requiring immediate containment. Over the past year of operations, no material security incidents or data breaches impacting the gateway environment or connectivity have occurred.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation periodically validates its incident handling readiness through targeted technical walkthroughs and infrastructure resilience testing. Rather than conducting large corporate mock drills, our compact technical team reviews threat scenarios directly against the production layout. This includes simulating network anomalies to verify that the IDS alerts trigger properly, evaluating firewall adjustment speed, and testing service availability zones to ensure the platform remains stable and responsive during emergency mitigation.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Security and operational logs are recorded in real-time across the gateway environment. Core security layers—including the network IDS, Coraza Web Application Firewall (WAF), HAProxy reverse proxy, and Linux system logs—are natively configured to track activity and detect anomalies. High-priority events, such as threat signature matches or authentication failures, instantly trigger alerts that are routed directly to the technical team for immediate review and corrective action.
+    <t>Yes. Firewall rule changes are managed through a structured technical review process. Any modification is evaluated internally by the core technical team to verify its security impact before implementation. Rule adjustments are tracked transparently via automated configuration version histories, system event tracking, and cloud activity logs. Post-deployment, the running configuration is verified to ensure intended connectivity is achieved without introducing unintended exposure.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf
+Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Real-time alerts are configured to flag boundary anomalies, potential firewall policy violations, and irregular system activities. Technical threat events and infrastructure health spikes automatically generate notifications that route directly to the core engineering team. Accountability for reviewing, containing, and resolving these alerts is clearly assigned within our technical team, ensuring that any high-priority security signal is acted upon immediately.
 Evidence Filed As: 
 POL006-Logging and Monitoring Policy.pdf
 SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. The organisation maintains a clear communication procedure to notify GSTN promptly if an incident carries potential external impact. For swift coordination, designated management personnel act as the primary Single Point of Contact (SPOC) to handle external escalations. While the technical team isolates and remediates the system, management directly shares necessary technical details and operational updates with the GSTN helpdesk through official communication channels.
-Evidence Filed As: 
-POL012-Incident Response Policy.pdf
-SOP005-Incident Response Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation ensures that all non-conformities (NCs) or observations raised during audits or assessments are tracked and closed within the mandated 45-day window, or as specified by GSTN. Any reported observation is directly reviewed by the core technical team to implement necessary security or infrastructure fixes. The remediation steps are thoroughly verified post-implementation to guarantee compliance and ensure swift, permanent closure of the item.
-Evidence Filed As: 
-POL009-Vulnerability Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The gateway firewall and network IDS layer are configured to inspect incoming traffic streams and generate immediate alerts for any anomalies or threat signature matches. Real-time logging is active for all traffic interacting with the production network zones, ensuring that high-priority security events trigger notifications instantly. These alerts are routed directly to the technical team for rapid review and administrative intervention..
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The gateway environment is deployed using a strictly segmented network architecture separated into isolated functional zones. Traffic is partitioned into distinct layers, including an external public DMZ for proxy routing, a private application zone for core computing, and a highly restricted trusted database zone. Ingress and egress network boundaries are controlled using firewall policies and security groups, ensuring that backend databases are never directly exposed to the internet. Administrative access is limited via dedicated secure VPN pathways.
+    <t>Yes. The architecture employs a tiered defense strategy to protect the firewall devices against DoS and DDoS threats. At the outer perimeter, native cloud infrastructure protection automatically intercepts and absorbs large-scale volumetric network floods (Layers 3 and 4) before they reach the environment. Directly behind this edge, network security groups act as an immediate packet filter, allowing inbound traffic strictly on designated entry points (TCP 80, TCP 443, and UDP 31248) while dropping all other unauthorized port probes automatically. Finally, the firewall devices and reverse proxy layers enforce strict connection rate-limiting and state-tracking thresholds to block application-layer (Layer 7) resource exhaustion attempts.
 Evidence Filed As: 
 POL004-Network Security Policy.pdf
 Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
   </si>
   <si>
-    <t>Yes. The core technical team is directly responsible for managing, updating, and maintaining the firewall rule sets. Configurations are controlled electronically via the firewall administration layer and host-level security groups. Any proposed rule change undergoes an internal peer-review process within the team to ensure security alignment before deployment. The running configuration is reviewed periodically to identify and prune redundant or obsolete rules, with automated configuration versioning providing a clean audit trail.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf
-Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
-  </si>
-  <si>
-    <t>No. The firewall configuration does not contain any rules that allow unauthorized traffic. Perimeter access is governed by a strict default-deny policy, meaning all unsolicited incoming traffic is blocked automatically. Inbound access is permitted exclusively via explicit allowlist rules tailored to validated endpoints and necessary communication ports. The core technical team reviews these access rules periodically to ensure that obsolete or unverified source IPs are instantly removed.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf
-Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Firewall rule changes are managed through a structured technical review process. Any modification is evaluated internally by the core technical team to verify its security impact before implementation. Rule adjustments are tracked transparently via automated configuration version histories, system event tracking, and cloud activity logs. Post-deployment, the running configuration is verified to ensure intended connectivity is achieved without introducing unintended exposure.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf
-Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Firewall logs are continuously collected and stored within a secure, access-restricted environment. To protect log integrity, access to these records is strictly confined to authorized technical personnel. The infrastructure utilizes an automated log distribution and rotation policy where standard operational logs are maintained for immediate troubleshooting, while high-priority security and network access events are archived securely for long-term compliance and forensic audit requirements.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. In the absence of a traditional enterprise SIEM, the organisation utilizes a unified system monitoring framework that functions as an equivalent log aggregation layer. Firewall logs, Firewall alerts, and system events are continuously streamed to a centralized logging environment where automated parsers analyze traffic patterns against predefined threat signatures. Any anomalous spike or high-priority security event automatically triggers immediate administrative alerts, allowing the technical team to investigate and respond without manual daily console filtering.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The gateway infrastructure is configured to automatically detect, block, and flag unauthorized access attempts or anomalous traffic patterns. Security layers at both the network boundary and the application ingress monitor incoming requests for suspicious activity, such as brute-force attempts, network scanning, or malicious payloads. When a threat signature is triggered, the system blocks the traffic and instantly generates a high-priority alert, which is escalated directly to the technical team for immediate containment and review.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Real-time alerts are configured to flag boundary anomalies, potential firewall policy violations, and irregular system activities. Technical threat events and infrastructure health spikes automatically generate notifications that route directly to the core engineering team. Accountability for reviewing, containing, and resolving these alerts is clearly assigned within our technical team, ensuring that any high-priority security signal is acted upon immediately.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The architecture employs a tiered defense strategy to protect the firewall devices against DoS and DDoS threats. At the outer perimeter, native cloud infrastructure protection automatically intercepts and absorbs large-scale volumetric network floods (Layers 3 and 4) before they reach the environment. Directly behind this edge, network security groups act as an immediate packet filter, allowing inbound traffic strictly on designated entry points (TCP 80, TCP 443, and UDP 31248) while dropping all other unauthorized port probes automatically. Finally, the firewall devices and reverse proxy layers enforce strict connection rate-limiting and state-tracking thresholds to block application-layer (Layer 7) resource exhaustion attempts.
-Evidence Filed As: 
-POL004-Network Security Policy.pdf
-Annexure C-Infrastructure Security &amp; Operational Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. All user-facing application interfaces and API endpoints are strictly encrypted using HTTPS over TLS 1.2 or higher. Administrative traffic and remote engineering access are entirely secured using high-strength encrypted tunnels through a dedicated secure VPN gateway. Cryptographic certificates are automatically managed and renewed regularly to prevent expiration issues, ensuring that all external data-in-transit remains fully encrypted and compliant with required security standards.
-Evidence Filed As:
-Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. All data transmitted over public networks is fully encrypted using HTTPS over TLS 1.2 or TLS 1.3. The ingress proxy layer enforces high-strength cryptographic cipher suites, utilizing robust algorithms including AES-256 in Galois/Counter Mode (GCM) to safeguard public data integrity and confidentiality. Administrative network traffic is entirely constrained within strongly encrypted tunnels via a secure VPN gateway utilizing modern ChaCha20-Poly1305 cryptographic primitives. All cryptographic keys and configurations are handled natively through secure management practices to ensure strong protection against eavesdropping or tampering.
-Evidence Filed As: 
-Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Network encryption protocols and transport layer configurations are periodically tested and validated through automated vulnerability assessment scans and internal configuration reviews. The ingress proxy boundaries are audited to verify that legacy protocols and weak cipher suites are disabled, enforcing a strict baseline of TLS 1.2 or higher using authenticated encryption algorithms like AES-256-GCM. Any observation or potential configuration divergence identified during these routine security tests is promptly assessed and remediated by the technical team.
-Evidence Filed As: 
-Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Transport layer encryption is strictly maintained across all public-facing interfaces and administrative access channels using TLS 1.2/1.3 and secure VPN tunnels. Internal data routing is entirely contained within isolated private network segments that are completely cut off from direct internet exposure. The integrity of these network segments is continuously validated through automated boundary logs and system alert rules, ensuring any configuration anomalies or potential exposure lapses are flagged instantly for technical review.
-Evidence Filed As: 
-Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf</t>
-  </si>
-  <si>
-    <t>No. The GSP platform does not utilize any legacy, end-of-life (EOL), or out-of-support hardware or software components within the infrastructure interfacing with the GST System. The environment is built entirely on modern, cloud-native virtual instances running actively supported Linux distributions and contemporary software frameworks. All packages, proxy binaries, and cryptographic layers are regularly updated to ensure zero dependency on legacy systems.
-Evidence Filed As: 
-POL005-Infrastructure Security Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The core internal technical team directly owns the ongoing maintenance, administration, and system-level support for all hardware instances and software layers interfacing with the GST Systems. The team monitors system health, applies security upgrades, and manages integration components without relying on external third-party service providers. This dedicated internal structure ensures rapid incident troubleshooting and full operational control over the compliance perimeter.
-Evidence Filed As: 
-BSL-Roles Responsibilities Access Matrix.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The internal technical team maintains an updated inventory of all virtualized infrastructure instances and software components dedicated to GST compliance operations. Since the platform operates entirely on cloud infrastructure, hardware and compute assets are recorded via continuous cloud service inventories. Software dependencies and runtime framework packages are tracked through code configuration parameters and license management records, ensuring all application subscriptions remain current and valid.
-Evidence Filed As: 
-BSL-Production_Technology_Inventory.xlsx</t>
-  </si>
-  <si>
     <t>Yes. System hardening is enforced at all operational layers using a standardized security configuration baseline. Because the environment is cloud-virtualized, base operating system images are strictly minimized to eliminate unnecessary background services, protocols, and default binaries. Network interfaces on individual compute nodes are hardened by restricting inbound access to designated secure loops, while application runtimes and databases are bound strictly to internal addresses. System deployment configurations are routinely audited against established internal checklists to ensure no operational drift occurs.
 Evidence Filed As: 
 POL004-Network Security Policy.pdf</t>
@@ -1195,21 +1084,6 @@
   </si>
   <si>
     <t>The platform operates on a 100% cloud-hosted deployment model and does not own, manage, or occupy any physical server rooms or data center spaces. Because there is no physical operational perimeter under our management, physical system security reviews are not applicable to our deployment scope. The internal security review process focuses entirely on logical access monitoring, infrastructure boundaries, and credential safeguards.</t>
-  </si>
-  <si>
-    <t>Yes. The platform designates an internal technical lead to serve as the active Single Point of Contact (SPOC) for all interactions with GSTN and the MSP. Availability protocols are formally established, ensuring direct engineering-level communication and swift technical coordination for any operational, integration, or troubleshooting requirements.
-Evidence Filed As: 
-BSL-GSTN Communication and SPOC Directory.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Technical roles, operational duties, and interface responsibilities for coordinating with GSTN and the MSP are formally defined and documented within the platform's compliance governance framework. The documentation clearly outlines the specific operational scope and communication mandates assigned to the designated technical SPOC to ensure seamless accountability.
-Evidence Filed As: 
-BSL-GSTN Communication and SPOC Directory.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Project governance roles and designated technical SPOC records are reviewed annually and updated immediately during any operational restructuring or team alignment. This process ensures that internal compliance documentation remains accurate and reflects current engineering points of contact without administrative delay.
-Evidence Filed As: 
-BSL-GSTN Communication and SPOC Directory.pdf</t>
   </si>
   <si>
     <t>Yes. Role-Based Access Control (RBAC) is strictly enforced across the infrastructure and gateway layers. System access rights are provisioned strictly on a need-to-know basis, mapping privileges directly to functional roles (such as deployment execution versus read-only telemetry monitoring). Administrative capabilities are heavily restricted, ensuring that service boundaries are maintained without exposing backend system access to unauthorized endpoints.
@@ -1236,128 +1110,36 @@
 SOP002-User &amp; Credential Management Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. Multi-factor authentication (MFA) is strictly mandatory and enforced for all administrative access channels and critical cloud management layers. Access to backend environments requires valid multi-factor verification alongside primary system credentials. No external partners or third parties are granted access to the production environment.
-Evidence Filed As: 
-POL003-Password Credential Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. A technical risk assessment is conducted annually to identify and mitigate potential security threats across the platform's infrastructure and application layers. The findings are documented internally to ensure continuous security alignment.
-Evidence Filed As: 
-BSL-Information Security Assessment.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Identified technical risks are tracked within a simplified internal risk registry. Mitigation actions, such as configuration tuning and security patch deployments, are assigned directly to the engineering team and tracked until closure based on severity.
-Evidence Filed As: 
-BSL-Information Security Assessment.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Third-party risk evaluation is strictly confined to our tier-1 enterprise providers: our cloud infrastructure host and Tata Communications Limited (TCL) for managed MPLS-GSTN network connectivity. The platform handles zero downstream operations through external software contractors or manual service vendors, ensuring a highly contained risk boundary.
-Evidence Filed As: 
-POL011-ASP Onboarding &amp; Lifecycle Management Policy.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Backup copies are securely stored in redundant cloud object storage distributed across other Availability Zone (AZ) locations. This ensures full geographic isolation and absolute data durability against any localized infrastructure or datacenter failures.
+    <t>Yes. Backup restoration procedures are fully documented, and recovery integrity is validated continuously via our real-time standby replication architecture. This setup ensures instant data availability and failover readiness without operational downtime.
 Evidence Filed As: 
 POL007-Backup and Recovery Policy.pdf
 SOP004-Backup &amp; Recovery Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. All backup data is automatically encrypted at rest using industry-standard AES-256 encryption. Access to the backup storage tier is strictly restricted through secure access permissions to prevent unauthorized access.
+    <t>Yes. The automated backup lifecycle captures the entire system state. Because application configurations and environment settings are maintained natively within the database layer, a single unified backup ensures complete, consistent, and absolute system restoration.
 Evidence Filed As: 
 POL007-Backup and Recovery Policy.pdf
 SOP004-Backup &amp; Recovery Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. Backup restoration procedures are fully documented, and recovery integrity is validated continuously via our real-time standby replication architecture. This setup ensures instant data availability and failover readiness without operational downtime.
-Evidence Filed As: 
-POL007-Backup and Recovery Policy.pdf
-SOP004-Backup &amp; Recovery Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Data backup retention periods are strictly defined based on operational requirements. Archival lifecycles and data purging are handled through automated, system-enforced storage policies to ensure predictable and secure data disposal.
-Evidence Filed As: 
-POL007-Backup and Recovery Policy.pdf
-SOP004-Backup &amp; Recovery Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The automated backup lifecycle captures the entire system state. Because application configurations and environment settings are maintained natively within the database layer, a single unified backup ensures complete, consistent, and absolute system restoration.
-Evidence Filed As: 
-POL007-Backup and Recovery Policy.pdf
-SOP004-Backup &amp; Recovery Procedure.pdf</t>
-  </si>
-  <si>
     <t>Yes. Comprehensive audit logging is natively maintained across all application, database, and infrastructure layers. The system automatically captures user access, configuration changes, and critical operational events to provide a tamper-resistant security trail for monitoring and investigations.
 Evidence Filed As: 
 POL006-Logging and Monitoring Policy.pdf
 SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. System, application, and database logs are securely retained and archived using automated cloud lifecycle retention policies. Access to historical log stores is strictly restricted to prevent unauthorized modification or tampering.
+    <t>Yes. Platform logs and system telemetry are continuously monitored using automated alerting rules to detect anomalies, unauthorized access attempts, or suspicious spikes. Security events trigger instant automated notifications directly to the core engineering team for immediate evaluation.
 Evidence Filed As: 
 POL006-Logging and Monitoring Policy.pdf
 SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. Platform logs and system telemetry are continuously monitored using automated alerting rules to detect anomalies, unauthorized access attempts, or suspicious spikes. Security events trigger instant automated notifications directly to the core engineering team for immediate evaluation.
+    <t>Yes. Access to all operational and system logs is strictly restricted to authorized technical personnel on a read-only basis. The underlying log storage tier enforces absolute immutability, ensuring that historical log data cannot be modified or deleted by any account.
 Evidence Filed As: 
 POL006-Logging and Monitoring Policy.pdf
 SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
   </si>
   <si>
-    <t>Yes. Automated, real-time alerting mechanisms are configured across critical infrastructure and application endpoints. High-severity events, such as authentication anomalies or anomalous traffic spikes, trigger instant system notifications routed directly to the engineering team.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Access to all operational and system logs is strictly restricted to authorized technical personnel on a read-only basis. The underlying log storage tier enforces absolute immutability, ensuring that historical log data cannot be modified or deleted by any account.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. System, network, and application telemetry are centrally consolidated within a unified cloud monitoring environment. All events are tracked against synchronized timestamps, allowing seamless end-to-end traceability and analysis across the entire infrastructure.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The platform automatically maintains comprehensive audit trails for all critical actions, system modifications, and database changes. Every single entry is permanently recorded with a synchronized timestamp, ensuring complete traceability and absolute accountability during security reviews.
-Evidence Filed As: 
-POL006-Logging and Monitoring Policy.pdf
-SOP007-Log Monitoring &amp; Review Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. The organisation undergoes formal independent external security compliance reviews on an annual basis. These assessments are aligned with ISO 27001 standard practices and regulatory mandates to verify our overall security posture.
-Evidence Filed As: 
-BSL-ISO Certificate.pdf
-BSL-VAPT Audit Report.pdf</t>
-  </si>
-  <si>
-    <t>Yes. All final audit reports, official certificates, and compliance letters from the external auditors are safely stored as final proof.
-Evidence Filed As: 
-BSL-ISO Certificate
-BSL-VAPT Audit Report</t>
-  </si>
-  <si>
-    <t>Yes. The external audit reviews strictly follow standard international frameworks, fully aligning with the requirements of the ISO 27001 certification.
-Evidence Filed As: 
-BSL-ISO Certificate
-BSL-VAPT Audit Report</t>
-  </si>
-  <si>
-    <t>Yes. Our external security audits conclude with formal compliance documentation. The platform holds a valid ISO 27001 certificate, and our core application security is validated via a VAPT report issued by a CERT-In empanelled auditor.
-Evidence Filed As: 
-BSL-ISO Certificate
-BSL-VAPT Audit Report</t>
-  </si>
-  <si>
-    <t>Yes. Any technical observations identified during the VAPT exercise are resolved directly before the final sign-off and issuance of the clean audit report.
-Evidence Filed As: 
-BSL-ISO Certificate
-BSL-VAPT Audit Report</t>
-  </si>
-  <si>
     <t>Yes. The Privacy Policy is prominently published on the official application website and is fully accessible to all users. The platform is strictly operated in compliance with this policy to ensure complete data protection.
 Evidence Filed As: 
 POL001-Information Security Policy.pdf</t>
@@ -1384,30 +1166,6 @@
 SOP005-Incident Response Procedure.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes. Ongoing compliance is ensured through two distinct layers: continuous platform monitoring is managed internally via a centralized system, while regular independent verification is conducted through our annual ISO 27001 and external VAPT audit cycles.
-Evidence Filed As: 
-POL001-Information Security Policy.pdf
-POL006-Logging and Monitoring Policy.pdf
-BSL-ISO Certificate
-BSL-VAPT Audit Report
-</t>
-  </si>
-  <si>
-    <t>Yes. Application-layer Vulnerability Assessment and Penetration Testing (VAPT) is regularly conducted by a CERT-In empanelled security auditor. The assessment fully covers the core application interfaces and all exposed API endpoints utilized by connecting ASP applications within the platform's operational scope.
-Evidence Filed As: 
-SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. All technical findings from the VAPT exercise are formally documented by the external security auditor. The final VAPT report explicitly details both the initial observations and the subsequent validation proofs showing that all identified vulnerabilities were successfully resolved.
-Evidence Filed As: 
-SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf</t>
-  </si>
-  <si>
-    <t>Yes. Any critical or high-severity vulnerabilities identified during the VAPT process are resolved immediately. A formal re-testing exercise is conducted by the CERT-In empanelled auditor to independently verify and confirm all fixes before the final clean report is issued.
-Evidence Filed As: 
-SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf</t>
-  </si>
-  <si>
     <t>Yes. Independent Penetration Testing (PT) simulating real-world attack scenarios is conducted by a CERT-In empanelled auditor. The exercise targets the core application interfaces and all exposed API endpoints utilized by connecting ASP applications to identify and close any exploitable security flaws before final sign-off.
 Evidence Filed As: 
 SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf</t>
@@ -1459,11 +1217,6 @@
   </si>
   <si>
     <t>Not applicable as no external third-party ASP applications are onboarded to consume GSP APIs at present. The requirement to submit annual compliance certificates will apply to external parties upon onboarding.</t>
-  </si>
-  <si>
-    <t>Yes. The platform operates as a stateless, pass-through gateway. Inbound transactions are authenticated via server-side API Key Authentication credential validation, securely mapped to the corresponding GST System credentials, and routed to the GSTN APIs in real-time. Payload data is processed transiently within volatile memory during the request lifecycle and is never persistently stored, cached, or modified within the GSP layer.
-Evidence Filed As: 
-Annexure A-GSP Platform Architecture.pdf</t>
   </si>
   <si>
     <t>Yes. The organisation operates a designated cloud-based application, Octa GST, to deliver compliance services to end customers. Architecturally, this application is completely isolated from the core GSP gateway tier and communicates exclusively as an external client via secured outbound API endpoints. The GSP layer evaluates all incoming requests from this application using identical API Key Authentication credential validation, logical routing separation, and same controls as applied to any external application profile.
@@ -1486,6 +1239,293 @@
   <si>
     <t>Yes. The on-premise facility housing the GSP team for development, testing, and operational activities is located within a premium commercial complex featuring gated campus entry, trained security guards, integrated CCTV surveillance loops, and automated central fire alarm systems.
 These physical safety and security infrastructures are fully covered under a comprehensive professional maintenance and governance framework managed by the complex facility administration. This infrastructure uptime is fully funded via our mandatory monthly Common Area Maintenance (CAM) charges, ensuring continuous preventive testing and operational effectiveness.</t>
+  </si>
+  <si>
+    <t>Secure MPLS connectivity for direct integration with the GST System is provisioned via Tata Communications Limited (TCL), the designated Internet Service Provider (ISP). The dedicated network connection is maintained and monitored in accordance with official GSTN connectivity guidelines to ensure reliable, high-availability data routing. The organisation maintains a valid enterprise service level agreement with the provider covering operational support and bandwidth availability for the production GSP gateway environment.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf
+Annexure C-Infrastructure Security &amp; Operational Controls.pdf
+TCL-Contract-OrderForm.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation enforces a streamlined incident response procedure to manage security events flagged by the network IDS layer. Once an alert is verified as a valid security threat by our administration team, containment protocols are launched immediately to patch and protect the perimeter. If an event impacts or threatens the integrity of external connections, a formal notification protocol is initiated to communicate the operational details directly to the GSTN helpdesk or technical support authorities through designated security management channels.
+Evidence Filed As: 
+SOP005-Incident Response Procedure.pdf
+BSL-Contact Directory.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The GSP production environment monitors for potential Command-and-Control (C&amp;C) activity through strict network isolation and active signature tracking. The infrastructure is segmented into distinct, isolated security zones (DMZ, Application, and Database layers) using AWS Security Groups to prevent lateral exposure across systems.
+Traffic across these network zones is continuously analyzed by the network IDS layer, which is explicitly configured with active botcc (Botnet Command and Control) signature rules. This mechanism inspects network packet streams and triggers immediate, high-priority administrative alerts if any data patterns match known malicious C&amp;C infrastructure.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf
+Technical Implementation Demonstration.pdf (Section 2)</t>
+  </si>
+  <si>
+    <t>Yes. The organisation enforces a structured patch management program to ensure all production servers and infrastructure components receive regular security updates. Security advisories from operating system vendors, software dependencies, and authoritative bodies like CERT-In are periodically reviewed by the administration team to evaluate relevance and risk. Applicable patches are verified and tested in a controlled environment before being deployed during scheduled maintenance windows to maintain system stability and platform availability.
+Evidence Filed As: 
+SOP008-Patch &amp; Security Update Procedure.pdf
+POL009-Vulnerability Management Policy.pdf
+Technical Implementation Demonstration.pdf (Section 19)</t>
+  </si>
+  <si>
+    <t>Yes. The platform operates as a stateless, pass-through gateway. Inbound transactions are authenticated via server-side API Key Authentication credential validation, securely mapped to the corresponding GST System credentials, and routed to the GSTN APIs in real-time. Payload data is processed transiently within volatile memory during the request lifecycle and is never persistently stored, cached, or modified within the GSP layer.
+Evidence Filed As: 
+Annexure A-GSP Platform Architecture.pdf
+Technical Implementation Demonstration.pdf (Section 1)</t>
+  </si>
+  <si>
+    <t>Yes. Security and operational logs are recorded in real-time across the gateway environment. Core security layers—including the network IDS, Coraza Web Application Firewall (WAF), HAProxy reverse proxy, and Linux system logs—are natively configured to track activity and detect anomalies. High-priority events, such as threat signature matches or authentication failures, instantly trigger alerts that are routed directly to the technical team for immediate review and corrective action.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 9)</t>
+  </si>
+  <si>
+    <t>Yes. The organisation maintains a clear communication procedure to notify GSTN promptly if an incident carries potential external impact. For swift coordination, designated management personnel act as the primary Single Point of Contact (SPOC) to handle external escalations. While the technical team isolates and remediates the system, management directly shares necessary technical details and operational updates with the GSTN helpdesk through official communication channels.
+Evidence Filed As: 
+POL012-Incident Response Policy.pdf
+SOP005-Incident Response Procedure.pdf
+BSL-Contact Directory.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The gateway environment is deployed using a strictly segmented network architecture separated into isolated functional zones. Traffic is partitioned into distinct layers, including an external public DMZ for proxy routing, a private application zone for core computing, and a highly restricted trusted database zone. Ingress and egress network boundaries are controlled using firewall policies and security groups, ensuring that backend databases are never directly exposed to the internet. Administrative access is limited via dedicated secure VPN pathways.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf
+Annexure C-Infrastructure Security &amp; Operational Controls.pdf
+Technical Implementation Demonstration.pdf (Section 2, Section 3)</t>
+  </si>
+  <si>
+    <t>No. The firewall configuration does not contain any rules that allow unauthorized traffic. Perimeter access is governed by a strict default-deny policy, meaning all unsolicited incoming traffic is blocked automatically. Inbound access is permitted exclusively via explicit allowlist rules tailored to validated endpoints and necessary communication ports. The core technical team reviews these access rules periodically to ensure that obsolete or unverified source IPs are instantly removed.
+Evidence Filed As: 
+POL004-Network Security Policy.pdf
+Annexure C-Infrastructure Security &amp; Operational Controls.pdf
+Technical Implementation Demonstration.pdf (Section 5)</t>
+  </si>
+  <si>
+    <t>Request mapping is executed entirely server-side based on the identifier of each incoming API request. When a request hits the gateway, the GSP layer validates the HTTP Basic Authentication credentials presented in the header. The verified identity parameter is immediately used by the server runtime to dynamically look up and map the request context to the corresponding, isolated GSP credential set inside the secure environment memory block. This runtime mapping ensures that the incoming API request is securely processed and routed to the GST System over an encrypted HTTPS connection without exposing any backend credential records.
+Evidence Filed As: 
+Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf
+Technical Implementation Demonstration.pdf (Section 5)</t>
+  </si>
+  <si>
+    <t>Yes. Firewall logs are continuously collected and stored within a secure, access-restricted environment. To protect log integrity, access to these records is strictly confined to authorized technical personnel. The infrastructure utilizes an automated log distribution and rotation policy where standard operational logs are maintained for immediate troubleshooting, while high-priority security and network access events are archived securely for long-term compliance and forensic audit requirements.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 10)</t>
+  </si>
+  <si>
+    <t>Yes. The gateway firewall and network IDS layer are configured to inspect incoming traffic streams and generate immediate alerts for any anomalies or threat signature matches. Real-time logging is active for all traffic interacting with the production network zones, ensuring that high-priority security events trigger notifications instantly. These alerts are routed directly to the technical team for rapid review and administrative intervention..
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 4 , Section 9)</t>
+  </si>
+  <si>
+    <t>Yes. In the absence of a traditional enterprise SIEM, the organisation utilizes a unified system monitoring framework that functions as an equivalent log aggregation layer. Firewall logs, Firewall alerts, and system events are continuously streamed to a centralized logging environment where automated parsers analyze traffic patterns against predefined threat signatures. Any anomalous spike or high-priority security event automatically triggers immediate administrative alerts, allowing the technical team to investigate and respond without manual daily console filtering.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 6, Section 11)</t>
+  </si>
+  <si>
+    <t>Yes. The gateway infrastructure is configured to automatically detect, block, and flag unauthorized access attempts or anomalous traffic patterns. Security layers at both the network boundary and the application ingress monitor incoming requests for suspicious activity, such as brute-force attempts, network scanning, or malicious payloads. When a threat signature is triggered, the system blocks the traffic and instantly generates a high-priority alert, which is escalated directly to the technical team for immediate containment and review.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 4)</t>
+  </si>
+  <si>
+    <t>Yes. All user-facing application interfaces and API endpoints are strictly encrypted using HTTPS over TLS 1.2 or higher. Administrative traffic and remote engineering access are entirely secured using high-strength encrypted tunnels through a dedicated secure VPN gateway. Cryptographic certificates are automatically managed and renewed regularly to prevent expiration issues, ensuring that all external data-in-transit remains fully encrypted and compliant with required security standards.
+Evidence Filed As:
+Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf
+Technical Implementation Demonstration.pdf (Section 12)</t>
+  </si>
+  <si>
+    <t>Yes. All data transmitted over public networks is fully encrypted using HTTPS over TLS 1.2 or TLS 1.3. The ingress proxy layer enforces high-strength cryptographic cipher suites, utilizing robust algorithms including AES-256 in Galois/Counter Mode (GCM) to safeguard public data integrity and confidentiality. Administrative network traffic is entirely constrained within strongly encrypted tunnels via a secure VPN gateway utilizing modern ChaCha20-Poly1305 cryptographic primitives. All cryptographic keys and configurations are handled natively through secure management practices to ensure strong protection against eavesdropping or tampering.
+Evidence Filed As: 
+Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf
+Technical Implementation Demonstration.pdf (Section 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes. Network encryption protocols and transport layer configurations are periodically tested and validated through automated vulnerability assessment scans and internal configuration reviews. The ingress proxy boundaries are audited to verify that legacy protocols and weak cipher suites are disabled, enforcing a strict baseline of TLS 1.2 or higher using authenticated encryption algorithms like AES-256-GCM. Any observation or potential configuration divergence identified during these routine security tests is promptly assessed and remediated by the technical team.
+Evidence Filed As: 
+Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf
+Blowbits-VAPT-Report.pdf
+Technical Implementation Demonstration.pdf (Section 13)
+</t>
+  </si>
+  <si>
+    <t>Yes. Transport layer encryption is strictly maintained across all public-facing interfaces and administrative access channels using TLS 1.2/1.3 and secure VPN tunnels. Internal data routing is entirely contained within isolated private network segments that are completely cut off from direct internet exposure. The integrity of these network segments is continuously validated through automated boundary logs and system alert rules, ensuring any configuration anomalies or potential exposure lapses are flagged instantly for technical review.
+Evidence Filed As: 
+Annexure B-Identity Api Security &amp; Cryptographic Controls.pdf
+Technical Implementation Demonstration.pdf (Section 14)</t>
+  </si>
+  <si>
+    <t>No. The GSP platform does not utilize any legacy, end-of-life (EOL), or out-of-support hardware or software components within the infrastructure interfacing with the GST System. The environment is built entirely on modern, cloud-native virtual instances running actively supported Linux distributions and contemporary software frameworks. All packages, proxy binaries, and cryptographic layers are regularly updated to ensure zero dependency on legacy systems.
+Evidence Filed As: 
+POL005-Infrastructure Security Policy.pdf
+Technical Implementation Demonstration.pdf (Section 15)
+BSL-Production_Technology_Inventory.xlsx</t>
+  </si>
+  <si>
+    <t>Yes. The internal technical team maintains an updated inventory of all virtualized infrastructure instances and software components dedicated to GST compliance operations. Since the platform operates entirely on cloud infrastructure, hardware and compute assets are recorded via continuous cloud service inventories. Software dependencies and runtime framework packages are tracked through code configuration parameters and license management records, ensuring all application subscriptions remain current and valid.
+Evidence Filed As: 
+Technical Implementation Demonstration.pdf (Section 15)
+BSL-Production_Technology_Inventory.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes. The core internal technical team directly owns the ongoing maintenance, administration, and system-level support for all hardware instances and software layers interfacing with the GST Systems. The team monitors system health, applies security upgrades, and manages integration components without relying on external third-party service providers. This dedicated internal structure ensures rapid incident troubleshooting and full operational control over the compliance perimeter.
+Evidence Filed As: 
+BSL-Roles Responsibilities Access Matrix.pdf
+</t>
+  </si>
+  <si>
+    <t>Yes. Multi-factor authentication (MFA) is strictly mandatory and enforced for all administrative access channels and critical cloud management layers. Access to backend environments requires valid multi-factor verification alongside primary system credentials. No external partners or third parties are granted access to the production environment.
+Evidence Filed As: 
+POL003-Password Credential Management Policy.pdf
+Technical Implementation Demonstration.pdf (Section 16)</t>
+  </si>
+  <si>
+    <t>Yes. Backup copies are securely stored in redundant cloud object storage distributed across other Availability Zone (AZ) locations. This ensures full geographic isolation and absolute data durability against any localized infrastructure or datacenter failures.
+Evidence Filed As: 
+POL007-Backup and Recovery Policy.pdf
+SOP004-Backup &amp; Recovery Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 17)</t>
+  </si>
+  <si>
+    <t>Yes. All backup data is automatically encrypted at rest using industry-standard AES-256 encryption. Access to the backup storage tier is strictly restricted through secure access permissions to prevent unauthorized access.
+Evidence Filed As: 
+POL007-Backup and Recovery Policy.pdf
+SOP004-Backup &amp; Recovery Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 14)</t>
+  </si>
+  <si>
+    <t>Yes. Data backup retention periods are strictly defined based on operational requirements. Archival lifecycles and data purging are handled through automated, system-enforced storage policies to ensure predictable and secure data disposal.
+Evidence Filed As: 
+POL007-Backup and Recovery Policy.pdf
+SOP004-Backup &amp; Recovery Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 17)</t>
+  </si>
+  <si>
+    <t>Yes. System, application, and database logs are securely retained and archived using automated cloud lifecycle retention policies. Access to historical log stores is strictly restricted to prevent unauthorized modification or tampering.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 11)</t>
+  </si>
+  <si>
+    <t>Yes. Automated, real-time alerting mechanisms are configured across critical infrastructure and application endpoints. High-severity events, such as authentication anomalies or anomalous traffic spikes, trigger instant system notifications routed directly to the engineering team.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 9)</t>
+  </si>
+  <si>
+    <t>Yes. System, network, and application telemetry are centrally consolidated within a unified cloud monitoring environment. All events are tracked against synchronized timestamps, allowing seamless end-to-end traceability and analysis across the entire infrastructure.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 11)</t>
+  </si>
+  <si>
+    <t>Yes. The platform automatically maintains comprehensive audit trails for all critical actions, system modifications, and database changes. Every single entry is permanently recorded with a synchronized timestamp, ensuring complete traceability and absolute accountability during security reviews.
+Evidence Filed As: 
+POL006-Logging and Monitoring Policy.pdf
+SOP007-Log Monitoring &amp; Review Procedure.pdf
+Technical Implementation Demonstration.pdf (Section 18)</t>
+  </si>
+  <si>
+    <t>Yes. Any technical observations identified during the VAPT exercise are resolved directly before the final sign-off and issuance of the clean audit report.
+Evidence Filed As: 
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Certificate.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Our external security audits conclude with formal compliance documentation. The platform holds a valid ISO 27001 certificate, and our core application security is validated via a VAPT report issued by a CERT-In empanelled auditor.
+Evidence Filed As: 
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Certificate.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The external audit reviews strictly follow standard international frameworks, fully aligning with the requirements of the ISO 27001 certification.
+Evidence Filed As: 
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Certificate.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. All final audit reports, official certificates, and compliance letters from the external auditors are safely stored as final proof.
+Evidence Filed As: 
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Certificate.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The organisation undergoes formal independent external security compliance reviews on an annual basis. These assessments are aligned with ISO 27001 standard practices and regulatory mandates to verify our overall security posture.
+Evidence Filed As: 
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Certificate.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Application-layer Vulnerability Assessment and Penetration Testing (VAPT) is regularly conducted by a CERT-In empanelled security auditor. The assessment fully covers the core application interfaces and all exposed API endpoints utilized by connecting ASP applications within the platform's operational scope.
+Evidence Filed As: 
+SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf
+Blowbits-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. All technical findings from the VAPT exercise are formally documented by the external security auditor. The final VAPT report explicitly details both the initial observations and the subsequent validation proofs showing that all identified vulnerabilities were successfully resolved.
+Evidence Filed As: 
+SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf
+Blowbits-Response-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Any critical or high-severity vulnerabilities identified during the VAPT process are resolved immediately. A formal re-testing exercise is conducted by the CERT-In empanelled auditor to independently verify and confirm all fixes before the final clean report is issued.
+Evidence Filed As: 
+SOP006-Vulnerability Assessment &amp; Remediation Procedure.pdf
+Blowbits-Response-VAPT-Report.pdf</t>
+  </si>
+  <si>
+    <t>Yes. The platform designates an internal technical lead to serve as the active Single Point of Contact (SPOC) for all interactions with GSTN and the MSP. Availability protocols are formally established, ensuring direct engineering-level communication and swift technical coordination for any operational, integration, or troubleshooting requirements.
+Evidence Filed As: 
+BSL-Contact Directory.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Technical roles, operational duties, and interface responsibilities for coordinating with GSTN and the MSP are formally defined and documented within the platform's compliance governance framework. The documentation clearly outlines the specific operational scope and communication mandates assigned to the designated technical SPOC to ensure seamless accountability.
+Evidence Filed As: 
+BSL-Contact Directory.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Project governance roles and designated technical SPOC records are reviewed annually and updated immediately during any operational restructuring or team alignment. This process ensures that internal compliance documentation remains accurate and reflects current engineering points of contact without administrative delay.
+Evidence Filed As: 
+BSL-Contact Directory.pdf</t>
+  </si>
+  <si>
+    <t>Yes. A technical risk assessment is conducted annually to identify and mitigate potential security threats across the platform's infrastructure and application layers. The findings are documented internally to ensure continuous security alignment.
+Evidence Filed As: 
+BSL-Information Security Risk Assessment.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Identified technical risks are tracked within a simplified internal risk registry. Mitigation actions, such as configuration tuning and security patch deployments, are assigned directly to the engineering team and tracked until closure based on severity.
+Evidence Filed As: 
+BSL-Information Security Risk Assessment.pdf</t>
+  </si>
+  <si>
+    <t>Yes. Third-party risk evaluation is strictly confined to our tier-1 enterprise providers: our cloud infrastructure host and Tata Communications Limited (TCL) for managed MPLS-GSTN network connectivity. The platform handles zero downstream operations through external software contractors or manual service vendors, ensuring +H70:H71a highly contained risk boundary.
+Evidence Filed As: 
+POL011-ASP Onboarding &amp; Lifecycle Management Policy.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes. Ongoing compliance is ensured through two distinct layers: continuous platform monitoring is managed internally via a centralized system, while regular independent verification is conducted through our annual ISO 27001 and external VAPT audit cycles.
+Evidence Filed As: 
+POL001-Information Security Policy.pdf
+POL006-Logging and Monitoring Policy.pdf
+Blowbits-ISO-27001.pdf
+Blowbits-VAPT-Report.pdf
+</t>
   </si>
 </sst>
 </file>
@@ -3081,10 +3121,10 @@
         <v>22</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" s="1" customFormat="1" ht="174" customHeight="1" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" s="1" customFormat="1" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="61"/>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -3098,7 +3138,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="2:8" s="1" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.2">
@@ -3117,7 +3157,7 @@
         <v>22</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="2:8" s="1" customFormat="1" ht="189" customHeight="1" x14ac:dyDescent="0.2">
@@ -3134,7 +3174,7 @@
         <v>22</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="1" customFormat="1" ht="160" x14ac:dyDescent="0.2">
@@ -3151,7 +3191,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="2:8" s="1" customFormat="1" ht="160" x14ac:dyDescent="0.2">
@@ -3168,7 +3208,7 @@
         <v>22</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="2:8" s="1" customFormat="1" ht="160" x14ac:dyDescent="0.2">
@@ -3185,7 +3225,7 @@
         <v>22</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="2:8" s="1" customFormat="1" ht="196" customHeight="1" x14ac:dyDescent="0.2">
@@ -3202,7 +3242,7 @@
         <v>22</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="2:8" s="1" customFormat="1" ht="160" x14ac:dyDescent="0.2">
@@ -3221,7 +3261,7 @@
         <v>22</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="1" customFormat="1" ht="144" x14ac:dyDescent="0.2">
@@ -3238,7 +3278,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3261,10 +3301,10 @@
         <v>22</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="160" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="176" x14ac:dyDescent="0.2">
       <c r="B15" s="63"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
@@ -3278,7 +3318,7 @@
         <v>22</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>270</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -3295,7 +3335,7 @@
         <v>22</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="165" customHeight="1" x14ac:dyDescent="0.2">
@@ -3318,7 +3358,7 @@
         <v>22</v>
       </c>
       <c r="H17" s="45" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -3335,7 +3375,7 @@
         <v>22</v>
       </c>
       <c r="H18" s="45" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -3358,7 +3398,7 @@
         <v>22</v>
       </c>
       <c r="H19" s="45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="128" x14ac:dyDescent="0.2">
@@ -3375,7 +3415,7 @@
         <v>22</v>
       </c>
       <c r="H20" s="45" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -3392,10 +3432,10 @@
         <v>22</v>
       </c>
       <c r="H21" s="45" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="160" x14ac:dyDescent="0.2">
       <c r="B22" s="63"/>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -3409,7 +3449,7 @@
         <v>22</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3432,7 +3472,7 @@
         <v>22</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3449,10 +3489,10 @@
         <v>22</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="192" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="208" x14ac:dyDescent="0.2">
       <c r="B25" s="34">
         <v>6</v>
       </c>
@@ -3472,7 +3512,7 @@
         <v>22</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="164" customHeight="1" x14ac:dyDescent="0.2">
@@ -3495,7 +3535,7 @@
         <v>22</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>281</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="176" x14ac:dyDescent="0.2">
@@ -3512,7 +3552,7 @@
         <v>22</v>
       </c>
       <c r="H27" s="45" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3529,7 +3569,7 @@
         <v>22</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
@@ -3552,7 +3592,7 @@
         <v>22</v>
       </c>
       <c r="H29" s="45" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3569,7 +3609,7 @@
         <v>22</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3586,7 +3626,7 @@
         <v>22</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3601,7 +3641,7 @@
         <v>22</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3618,7 +3658,7 @@
         <v>22</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3635,10 +3675,10 @@
         <v>22</v>
       </c>
       <c r="H34" s="45" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="166" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="63"/>
       <c r="C35" s="62"/>
       <c r="D35" s="62"/>
@@ -3652,10 +3692,10 @@
         <v>22</v>
       </c>
       <c r="H35" s="45" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="160" x14ac:dyDescent="0.2">
       <c r="B36" s="63">
         <v>9</v>
       </c>
@@ -3675,7 +3715,7 @@
         <v>22</v>
       </c>
       <c r="H36" s="45" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="149" customHeight="1" x14ac:dyDescent="0.2">
@@ -3692,10 +3732,10 @@
         <v>22</v>
       </c>
       <c r="H37" s="45" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="160" x14ac:dyDescent="0.2">
       <c r="B38" s="63">
         <v>10</v>
       </c>
@@ -3715,10 +3755,10 @@
         <v>22</v>
       </c>
       <c r="H38" s="45" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="160" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="176" x14ac:dyDescent="0.2">
       <c r="B39" s="63"/>
       <c r="C39" s="62"/>
       <c r="D39" s="62"/>
@@ -3732,7 +3772,7 @@
         <v>22</v>
       </c>
       <c r="H39" s="45" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -3749,7 +3789,7 @@
         <v>22</v>
       </c>
       <c r="H40" s="45" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -3766,7 +3806,7 @@
         <v>22</v>
       </c>
       <c r="H41" s="45" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="164" customHeight="1" x14ac:dyDescent="0.2">
@@ -3783,10 +3823,10 @@
         <v>22</v>
       </c>
       <c r="H42" s="45" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="175" customHeight="1" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="187" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="63"/>
       <c r="C43" s="62"/>
       <c r="D43" s="62"/>
@@ -3800,7 +3840,7 @@
         <v>22</v>
       </c>
       <c r="H43" s="45" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="157" customHeight="1" x14ac:dyDescent="0.2">
@@ -3817,10 +3857,10 @@
         <v>22</v>
       </c>
       <c r="H44" s="45" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="160" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="176" x14ac:dyDescent="0.2">
       <c r="B45" s="63"/>
       <c r="C45" s="62"/>
       <c r="D45" s="62"/>
@@ -3834,7 +3874,7 @@
         <v>22</v>
       </c>
       <c r="H45" s="45" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -3851,7 +3891,7 @@
         <v>22</v>
       </c>
       <c r="H46" s="45" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="192" x14ac:dyDescent="0.2">
@@ -3868,10 +3908,10 @@
         <v>22</v>
       </c>
       <c r="H47" s="45" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="128" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="144" x14ac:dyDescent="0.2">
       <c r="B48" s="63">
         <v>11</v>
       </c>
@@ -3891,10 +3931,10 @@
         <v>22</v>
       </c>
       <c r="H48" s="45" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="160" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="187" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="63"/>
       <c r="C49" s="62"/>
       <c r="D49" s="62"/>
@@ -3908,7 +3948,7 @@
         <v>22</v>
       </c>
       <c r="H49" s="45" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="167" customHeight="1" x14ac:dyDescent="0.2">
@@ -3925,10 +3965,10 @@
         <v>22</v>
       </c>
       <c r="H50" s="45" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="160" x14ac:dyDescent="0.2">
       <c r="B51" s="63"/>
       <c r="C51" s="62"/>
       <c r="D51" s="62"/>
@@ -3942,10 +3982,10 @@
         <v>22</v>
       </c>
       <c r="H51" s="45" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" ht="128" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="165" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="63">
         <v>12</v>
       </c>
@@ -3965,10 +4005,10 @@
         <v>22</v>
       </c>
       <c r="H52" s="45" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" ht="128" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="144" x14ac:dyDescent="0.2">
       <c r="B53" s="63"/>
       <c r="C53" s="62"/>
       <c r="D53" s="62"/>
@@ -3982,10 +4022,10 @@
         <v>22</v>
       </c>
       <c r="H53" s="45" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" ht="144" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="160" x14ac:dyDescent="0.2">
       <c r="B54" s="63"/>
       <c r="C54" s="62"/>
       <c r="D54" s="62"/>
@@ -3999,7 +4039,7 @@
         <v>22</v>
       </c>
       <c r="H54" s="45" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -4016,7 +4056,7 @@
         <v>22</v>
       </c>
       <c r="H55" s="45" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4039,7 +4079,7 @@
         <v>25</v>
       </c>
       <c r="H56" s="45" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="164" customHeight="1" x14ac:dyDescent="0.2">
@@ -4056,7 +4096,7 @@
         <v>22</v>
       </c>
       <c r="H57" s="45" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4073,7 +4113,7 @@
         <v>25</v>
       </c>
       <c r="H58" s="45" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4090,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="H59" s="45" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4113,7 +4153,7 @@
         <v>22</v>
       </c>
       <c r="H60" s="45" t="s">
-        <v>314</v>
+        <v>361</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4130,7 +4170,7 @@
         <v>22</v>
       </c>
       <c r="H61" s="45" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4147,7 +4187,7 @@
         <v>22</v>
       </c>
       <c r="H62" s="45" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
     </row>
     <row r="63" spans="2:8" ht="144" x14ac:dyDescent="0.2">
@@ -4170,7 +4210,7 @@
         <v>22</v>
       </c>
       <c r="H63" s="45" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4187,7 +4227,7 @@
         <v>22</v>
       </c>
       <c r="H64" s="45" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="128" x14ac:dyDescent="0.2">
@@ -4204,10 +4244,10 @@
         <v>22</v>
       </c>
       <c r="H65" s="45" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" ht="112" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="128" x14ac:dyDescent="0.2">
       <c r="B66" s="63"/>
       <c r="C66" s="62"/>
       <c r="D66" s="62"/>
@@ -4221,7 +4261,7 @@
         <v>22</v>
       </c>
       <c r="H66" s="45" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4238,7 +4278,7 @@
         <v>22</v>
       </c>
       <c r="H67" s="45" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4261,7 +4301,7 @@
         <v>22</v>
       </c>
       <c r="H68" s="45" t="s">
-        <v>322</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4276,7 +4316,7 @@
         <v>22</v>
       </c>
       <c r="H69" s="45" t="s">
-        <v>323</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4291,7 +4331,7 @@
         <v>22</v>
       </c>
       <c r="H70" s="45" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4317,7 +4357,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B72" s="63"/>
       <c r="C72" s="62"/>
       <c r="D72" s="62"/>
@@ -4331,10 +4371,10 @@
         <v>22</v>
       </c>
       <c r="H72" s="45" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B73" s="63"/>
       <c r="C73" s="62"/>
       <c r="D73" s="62"/>
@@ -4348,7 +4388,7 @@
         <v>22</v>
       </c>
       <c r="H73" s="45" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4365,10 +4405,10 @@
         <v>22</v>
       </c>
       <c r="H74" s="45" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B75" s="63"/>
       <c r="C75" s="62"/>
       <c r="D75" s="62"/>
@@ -4382,7 +4422,7 @@
         <v>22</v>
       </c>
       <c r="H75" s="45" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4399,7 +4439,7 @@
         <v>22</v>
       </c>
       <c r="H76" s="45" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4422,10 +4462,10 @@
         <v>22</v>
       </c>
       <c r="H77" s="45" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B78" s="63"/>
       <c r="C78" s="62"/>
       <c r="D78" s="62"/>
@@ -4439,7 +4479,7 @@
         <v>22</v>
       </c>
       <c r="H78" s="45" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4456,10 +4496,10 @@
         <v>22</v>
       </c>
       <c r="H79" s="45" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" ht="112" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" ht="128" x14ac:dyDescent="0.2">
       <c r="B80" s="63"/>
       <c r="C80" s="62"/>
       <c r="D80" s="62"/>
@@ -4473,7 +4513,7 @@
         <v>22</v>
       </c>
       <c r="H80" s="45" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4490,10 +4530,10 @@
         <v>22</v>
       </c>
       <c r="H81" s="45" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" ht="112" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" ht="128" x14ac:dyDescent="0.2">
       <c r="B82" s="63"/>
       <c r="C82" s="62"/>
       <c r="D82" s="62"/>
@@ -4507,10 +4547,10 @@
         <v>22</v>
       </c>
       <c r="H82" s="45" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" ht="112" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="128" x14ac:dyDescent="0.2">
       <c r="B83" s="63"/>
       <c r="C83" s="62"/>
       <c r="D83" s="62"/>
@@ -4524,10 +4564,10 @@
         <v>22</v>
       </c>
       <c r="H83" s="45" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B84" s="63">
         <v>19</v>
       </c>
@@ -4547,10 +4587,10 @@
         <v>22</v>
       </c>
       <c r="H84" s="45" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8" ht="80" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="97" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="63"/>
       <c r="C85" s="62"/>
       <c r="D85" s="62"/>
@@ -4564,10 +4604,10 @@
         <v>22</v>
       </c>
       <c r="H85" s="45" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="80" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="96" x14ac:dyDescent="0.2">
       <c r="B86" s="63"/>
       <c r="C86" s="62"/>
       <c r="D86" s="62"/>
@@ -4581,10 +4621,10 @@
         <v>22</v>
       </c>
       <c r="H86" s="45" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B87" s="63"/>
       <c r="C87" s="62"/>
       <c r="D87" s="62"/>
@@ -4598,10 +4638,10 @@
         <v>22</v>
       </c>
       <c r="H87" s="45" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" ht="80" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" ht="96" x14ac:dyDescent="0.2">
       <c r="B88" s="63"/>
       <c r="C88" s="62"/>
       <c r="D88" s="62"/>
@@ -4615,7 +4655,7 @@
         <v>22</v>
       </c>
       <c r="H88" s="45" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4638,7 +4678,7 @@
         <v>22</v>
       </c>
       <c r="H89" s="45" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4655,7 +4695,7 @@
         <v>22</v>
       </c>
       <c r="H90" s="45" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4672,7 +4712,7 @@
         <v>22</v>
       </c>
       <c r="H91" s="45" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4689,7 +4729,7 @@
         <v>22</v>
       </c>
       <c r="H92" s="45" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4706,7 +4746,7 @@
         <v>22</v>
       </c>
       <c r="H93" s="45" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="160" x14ac:dyDescent="0.2">
@@ -4723,7 +4763,7 @@
         <v>22</v>
       </c>
       <c r="H94" s="45" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="112" x14ac:dyDescent="0.2">
@@ -4746,10 +4786,10 @@
         <v>22</v>
       </c>
       <c r="H95" s="45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B96" s="63"/>
       <c r="C96" s="63"/>
       <c r="D96" s="62"/>
@@ -4763,10 +4803,10 @@
         <v>22</v>
       </c>
       <c r="H96" s="45" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" ht="112" x14ac:dyDescent="0.2">
       <c r="B97" s="63"/>
       <c r="C97" s="63"/>
       <c r="D97" s="62"/>
@@ -4780,7 +4820,7 @@
         <v>22</v>
       </c>
       <c r="H97" s="45" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4797,7 +4837,7 @@
         <v>22</v>
       </c>
       <c r="H98" s="45" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4814,7 +4854,7 @@
         <v>22</v>
       </c>
       <c r="H99" s="45" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4831,7 +4871,7 @@
         <v>22</v>
       </c>
       <c r="H100" s="45" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="96" x14ac:dyDescent="0.2">
@@ -4854,7 +4894,7 @@
         <v>22</v>
       </c>
       <c r="H101" s="45" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4871,7 +4911,7 @@
         <v>22</v>
       </c>
       <c r="H102" s="45" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="48" x14ac:dyDescent="0.2">
@@ -4888,7 +4928,7 @@
         <v>25</v>
       </c>
       <c r="H103" s="45" t="s">
-        <v>356</v>
+        <v>313</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4907,7 +4947,7 @@
         <v>22</v>
       </c>
       <c r="H104" s="45" t="s">
-        <v>357</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4924,7 +4964,7 @@
         <v>22</v>
       </c>
       <c r="H105" s="45" t="s">
-        <v>358</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="80" x14ac:dyDescent="0.2">
@@ -4941,7 +4981,7 @@
         <v>22</v>
       </c>
       <c r="H106" s="45" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="48" x14ac:dyDescent="0.2">
@@ -4960,7 +5000,7 @@
         <v>25</v>
       </c>
       <c r="H107" s="45" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="32" x14ac:dyDescent="0.2">
@@ -4977,7 +5017,7 @@
         <v>25</v>
       </c>
       <c r="H108" s="45" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="48" x14ac:dyDescent="0.2">
@@ -4994,7 +5034,7 @@
         <v>25</v>
       </c>
       <c r="H109" s="45" t="s">
-        <v>360</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="64" x14ac:dyDescent="0.2">
@@ -5125,21 +5165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1EFCA46C38A7647A52DC5B24481BA7E" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada70fd0749d2092e21ce48e49fd7d0e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5ef34df4-a1dc-4fb5-a797-e738f446dbed" xmlns:ns3="443fcf11-c07c-44e2-b1e3-23d23e7ef973" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8eaafda513be05b60e3164a1d1af7534" ns2:_="" ns3:_="">
     <xsd:import namespace="5ef34df4-a1dc-4fb5-a797-e738f446dbed"/>
@@ -5316,24 +5341,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B747C42A-6D39-4B8F-B519-E07CC6536547}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45CE55BD-F1D2-4125-9411-F07627B48344}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B31C149F-CBFA-4D01-B0EB-4DD4C260C103}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5352,6 +5375,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B747C42A-6D39-4B8F-B519-E07CC6536547}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45CE55BD-F1D2-4125-9411-F07627B48344}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
